--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Approval matrix and users'!$13:$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Document templates and prints'!$A$13:$K$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Document templates and prints'!$13:$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'E-mail wordings'!$A$13:$K$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'E-mail wordings'!$A$13:$K$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'E-mail wordings'!$13:$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Integration inputs from BDOI IT'!$A$13:$K$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Integration inputs from BDOI IT'!$13:$13</definedName>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIF('E-mail wordings'!J15:J83,"?*")</f>
+        <f>COUNTIF('E-mail wordings'!J15:J91,"?*")</f>
         <v/>
       </c>
       <c r="H27" s="15" t="inlineStr">
@@ -12416,7 +12416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Assignment moved to another user': trigger, recipients and text (Proposed).</t>
+          <t>Confirm the in-system notice 'Assignment moved to another user': trigger, recipients and text (Sent by BIBS).</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Weekly Placement Update Report available': trigger, recipients and text (Proposed).</t>
+          <t>Confirm the in-system notice 'Weekly Placement Update Report available': trigger, recipients and text (Sent by BIBS).</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Subject: Placement Update Report of &lt;dd-MMM-yyyy&gt;</t>
+          <t>Subject: PlacementUpdate_&lt;MMDDYYYY&gt;.xlsx generated</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr">
@@ -13860,8 +13860,432 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-20</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>NT-20 Package anniversary</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.017, BRPM.022</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-20); FRPM.004.01</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the in-system notice 'Package anniversary': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Subject: Package anniversary: &lt;risk code&gt;</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-21</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>NT-21 Product Matrix record for approval</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.003, BRPM.004, BRPM.022, PMADD01, PMADD02, PMADD07, PMADD08</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-21); FRPM.003.02</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the e-mail and in-system notice 'Product Matrix record for approval': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Subject: Product Matrix record for approval: &lt;risk code&gt;</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-22</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>NT-22 Package deactivation for approval</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.003, BRPM.004, BRPM.011, BRPM.022, PMADD01, PMADD02</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-22); FRPM.003.04</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the e-mail and in-system notice 'Package deactivation for approval': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Subject: &lt;deactivation request no.&gt;: deactivation of &lt;risk code&gt; for your approval</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-23</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>NT-23 Package deactivation decided</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.003, BRPM.004, BRPM.021, BRPM.022, PMADD01, PMADD02</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-23); FRPM.003.07</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the e-mail and in-system notice 'Package deactivation decided': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Subject: &lt;deactivation request no.&gt;: &lt;approved or rejected&gt;</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-24</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>NT-24 Insurers selected for the proposal</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.010, BRPM.013, BRPM.014, BRPM.022</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-24); FRPM.008.01</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the in-system notice 'Insurers selected for the proposal': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Subject: &lt;reference no.&gt;: Terms Agreed</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-25</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>NT-25 Proposal approved or returned</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.010, BRPM.013, BRPM.014, BRPM.022</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-25); FRPM.009.02</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the in-system notice 'Proposal approved or returned': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>Subject: &lt;reference no.&gt;: proposal &lt;approved or returned&gt; (to the requestor: &lt;reference no.&gt;: Proposal Ready)</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J39" s="15" t="n"/>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-26</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>NT-26 Client response recorded</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.010, BRPM.022</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-26); FRPM.010.01</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the in-system notice 'Client response recorded': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Subject: &lt;reference no.&gt;: client response &lt;Accepted, Rejected or Return for Revision&gt;</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>RC-EML-27</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>NT-27 Package deployment request</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.015, BRPM.022</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Annex P (NT-27); FRPM.015.01</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the in-system notice 'Package deployment request': trigger, recipients and text (Sent by BIBS).</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>'Approve as written' or the changed subject and text</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>Subject: Package deployment request &lt;deployment request no.&gt;</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J41" s="15" t="n"/>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A13:K33"/>
+  <autoFilter ref="A13:K41"/>
   <mergeCells count="5">
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B6:H6"/>
@@ -13869,7 +14293,7 @@
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="K15:K83">
+  <conditionalFormatting sqref="K15:K91">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Open"</formula>
     </cfRule>
@@ -13878,7 +14302,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="K15:K83" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value of the list Status (sheet Reference lists)." promptTitle="Status" prompt="Open, Received or Confirmed" type="list" errorStyle="stop">
+    <dataValidation sqref="K15:K91" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value of the list Status (sheet Reference lists)." promptTitle="Status" prompt="Open, Received or Confirmed" type="list" errorStyle="stop">
       <formula1>=LIST_STATUS</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -34,7 +34,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Lists of values'!$13:$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parameters and thresholds'!$A$13:$K$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Parameters and thresholds'!$13:$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Schedules and timings'!$A$13:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Schedules and timings'!$A$13:$K$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Schedules and timings'!$13:$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Approval matrix and users'!$A$13:$K$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Approval matrix and users'!$13:$13</definedName>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G24" s="20">
-        <f>COUNTIF('Schedules and timings'!J15:J71,"?*")</f>
+        <f>COUNTIF('Schedules and timings'!J15:J73,"?*")</f>
         <v/>
       </c>
       <c r="H24" s="19" t="inlineStr">
@@ -9380,7 +9380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Confirm the time (Thursday 08:00 (configurable)) and the recipients (TSU, Marketing) of the run: Generates and stores the Consolidated Placement Update Report; notice NT-17 (proposed)</t>
+          <t>Confirm the time (Thursday 08:00 for the last 7 days (settings of Annex J.7)) and the recipients (TSU, Marketing) of the run: Generates and stores the Consolidated Placement Update Report in the repository of Placement Update Reports; notice NT-17</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Thursday 08:00 (configurable)</t>
+          <t>Thursday 08:00 for the last 7 days (settings of Annex J.7)</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -10143,22 +10143,22 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>E-mail sending</t>
+          <t>Package deactivation</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>BRPM.012, BRPM.020, BRPM.021, BRPM.022</t>
+          <t>BRPM.003, BRPM.004, BRPM.006, BRPM.021, BRPM.022, PMADD01, PMADD02</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Annex R.2; FRPM.012.01, FRPM.027.01</t>
+          <t>Annex R.2; FRPM.003.05, FRPM.003.07</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Confirm the time (Every 2 minutes) and the recipients (-) of the run: Sends the queued e-mails (Quotation Slips, advisories, passwords) and records their status</t>
+          <t>Confirm the time (Daily 01:05) and the recipients (The requester; MBS) of the run: Deactivates the packages whose approved deactivation is effective today and queues the change for the product master transfer</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Every 2 minutes</t>
+          <t>Daily 01:05</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -10188,8 +10188,114 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>RC-SCH-06</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Product master transfer</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.022</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Annex R.2; FRPM.029.01</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the time (Every 30 minutes, and Send Now) and the recipients (MBS (Product Master Transfers screen)) of the run: Writes the waiting product master changes to the file ProductMaster_yyyyMMddHHmmss.csv for the receiving systems; a failure is alerted</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Day and time (Philippine time); recipients</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Every 30 minutes, and Send Now</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>RC-SCH-07</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>E-mail sending</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>BRPM.012, BRPM.020, BRPM.021, BRPM.022</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Annex R.2; FRPM.012.01, FRPM.027.01</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Confirm the time (Every 2 minutes) and the recipients (-) of the run: Sends the queued e-mails (Quotation Slips, advisories, passwords) and records their status</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Day and time (Philippine time); recipients</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Every 2 minutes</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Head, TSU</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A13:K21"/>
+  <autoFilter ref="A13:K23"/>
   <mergeCells count="5">
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B6:H6"/>
@@ -10197,7 +10303,7 @@
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="K15:K71">
+  <conditionalFormatting sqref="K15:K73">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1" stopIfTrue="1">
       <formula>"Open"</formula>
     </cfRule>
@@ -10206,7 +10312,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="K15:K71" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value of the list Status (sheet Reference lists)." promptTitle="Status" prompt="Open, Received or Confirmed" type="list" errorStyle="stop">
+    <dataValidation sqref="K15:K73" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value of the list Status (sheet Reference lists)." promptTitle="Status" prompt="Open, Received or Confirmed" type="list" errorStyle="stop">
       <formula1>=LIST_STATUS</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -910,7 +910,7 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>BIBS FRS-BDOI BRD-03 Product Maintenance v1.2</t>
+          <t>FRS BRD-03 Product Maintenance v1.2 in BDOI's template</t>
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Set up each package in force through a package request (type New or Update) with its signed slip and ManCom reference, validated before the map freeze; FR-PM-050 and FR-PM-051 are aligned in the next version of the set. BDOI confirms the number of packages so that TSU and MBS can plan the effort.</t>
+          <t>Set up each package in force through a package request (type New or Update) with its signed slip and ManCom reference, validated before the map freeze; FRPM.003.01, FRPM.003.03 and FRPM.024.02 are aligned in the next version of the set. BDOI confirms the number of packages so that TSU and MBS can plan the effort.</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>Criteria are kept only in Product Maintenance; computation and payout are specified in the Accounting, Operations and Collections sets, which reference the criteria codes (FR-PM-081 R2).</t>
+          <t>Criteria are kept only in Product Maintenance; computation and payout are specified in the Accounting, Operations and Collections sets, which reference the criteria codes (FRPM.018.02 R2).</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Each package in force at go-live is set up in BIBS through a package request (type New package, or Update for an existing risk code) with its signed package slip and ManCom reference, set up by MBS and validated before the map freeze; no package version is loaded by the data migration. FR-PM-050 rule R3 and FR-PM-051 rule R4 of release set v2.0 read as if the packages were loaded as version 1 by the migration; chapter 19 and template CI-06 say they are set up by request; this set takes the request route as its proposed position.</t>
+          <t>Each package in force at go-live is set up in BIBS through a package request (type New package, or Update for an existing risk code) with its signed package slip and ManCom reference, set up by MBS and validated before the map freeze; no package version is loaded by the data migration. FRPM.003.01, FRPM.003.03 rule R3 and FRPM.024.02 rule R4 of release set v2.0 read as if the packages were loaded as version 1 by the migration; chapter 19 and template CI-06 say they are set up by request; this set takes the request route as its proposed position.</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>BRPM.003 is a Must have. BRPM.013 is tested on the capture of insurer responses with their outcome and history (FR-PM-031); the comparative-table criteria are tested under BRPM.014 (FR-PM-034).</t>
+          <t>BRPM.003 is a Must have. BRPM.013 is tested on the capture of insurer responses with their outcome and history (FRPM.012.02, FRPM.012.03); the comparative-table criteria are tested under BRPM.014 (FRPM.012.02, FRPM.012.04).</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Use the proposed mandatory fields of FR-PM-020: request type, scope, package or programme name, product line, cover type (new package) or existing package, reason, requested terms, package end date and, when negotiated, at least one target insurer; a client only for client-specific packages.</t>
+          <t>Use the proposed mandatory fields of FRPM.011.02: request type, scope, package or programme name, product line, cover type (new package) or existing package, reason, requested terms, package end date and, when negotiated, at least one target insurer; a client only for client-specific packages.</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -843,7 +843,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BRD-03 Product Maintenance – what the Business Unit provides for the platform to work as specified in the FRS v1.2 (BDOI template)</t>
+          <t>BRD-03 Product Maintenance – what the Business Unit provides for the platform to work as specified in the FRS v1.3 (BDOI template)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>FRS BRD-03 Product Maintenance v1.2 in BDOI's template</t>
+          <t>FRS BRD-03 Product Maintenance v1.3 in BDOI's template</t>
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Where the item is in the FRS v1.2</t>
+          <t>Where the item is in the FRS v1.3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_Inputs_BRD-03_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:I31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -955,6 +956,7 @@
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
@@ -1002,6 +1004,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
@@ -1434,6 +1437,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
@@ -1616,6 +1620,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -3732,6 +3737,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -4620,6 +4626,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -5061,6 +5068,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -6232,6 +6240,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -7297,6 +7306,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -9475,6 +9485,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -10434,6 +10445,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -11605,6 +11617,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -12129,7 +12142,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Package Request Form layout: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>Package Request Form layout: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -12182,7 +12195,7 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Comparative Table: client output layout: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>Comparative Table: client output layout: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -12235,7 +12248,7 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Package slip layout: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>Package slip layout: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -12288,7 +12301,7 @@
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>ManCom approval record: confirm the standard layout: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>ManCom approval record: confirm the standard layout: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -12341,7 +12354,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Package advisory layout and wording: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>Package advisory layout and wording: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -12394,7 +12407,7 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Proposal Slip (non-package): confirm the layout: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>Proposal Slip (non-package): confirm the layout: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -12447,7 +12460,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Package reports: columns of the status, expiry and version history reports: the BDOI layout with wording and logo placement, or approval of the current BIBS layout shown in Annex Q.</t>
+          <t>Package reports: columns of the status, expiry and version history reports: the BDOI layout with wording and logo placement, or approval of the proposed layout shown in Annex Q.</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -12617,6 +12630,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
@@ -12982,7 +12996,7 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Package request moved to another stage': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Package request moved to another stage': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -13035,7 +13049,7 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Package available': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Package available': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -13088,7 +13102,7 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Package advisory (in-system)': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Package advisory (in-system)': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -13141,7 +13155,7 @@
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Package expired': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Package expired': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -13194,7 +13208,7 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail 'Package Quotation Slip to insurers': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail 'Package Quotation Slip to insurers': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -13247,7 +13261,7 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail 'Package advisory (e-mail)': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail 'Package advisory (e-mail)': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -13300,7 +13314,7 @@
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail (separate) 'Password of protected documents': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail (separate) 'Password of protected documents': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -13353,7 +13367,7 @@
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice and alert 'Package ending (expiry alert)': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice and alert 'Package ending (expiry alert)': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -13406,7 +13420,7 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice and alert 'Incentive rule to review': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice and alert 'Incentive rule to review': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -13459,7 +13473,7 @@
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Request assigned': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Request assigned': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -13512,7 +13526,7 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Confirm the alert 'Work item overdue': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the alert 'Work item overdue': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -13565,7 +13579,7 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Rate exception decided': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Rate exception decided': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -13724,7 +13738,7 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Assignment moved to another user': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Assignment moved to another user': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
@@ -13830,7 +13844,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Weekly Placement Update Report available': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Weekly Placement Update Report available': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
@@ -13883,7 +13897,7 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail 'Non-package Quotation Slip to insurers': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail 'Non-package Quotation Slip to insurers': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -13936,7 +13950,7 @@
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail 'Proposal to the client (non-package)': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail 'Proposal to the client (non-package)': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
@@ -13989,7 +14003,7 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Package anniversary': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Package anniversary': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
@@ -14042,7 +14056,7 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail and in-system notice 'Product Matrix record for approval': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail and in-system notice 'Product Matrix record for approval': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
@@ -14095,7 +14109,7 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail and in-system notice 'Package deactivation for approval': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail and in-system notice 'Package deactivation for approval': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -14148,7 +14162,7 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Confirm the e-mail and in-system notice 'Package deactivation decided': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the e-mail and in-system notice 'Package deactivation decided': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
@@ -14201,7 +14215,7 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Insurers selected for the proposal': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Insurers selected for the proposal': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -14254,7 +14268,7 @@
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Proposal approved or returned': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Proposal approved or returned': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr">
@@ -14307,7 +14321,7 @@
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Client response recorded': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Client response recorded': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -14360,7 +14374,7 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Confirm the in-system notice 'Package deployment request': trigger, recipients and text (Sent by BIBS).</t>
+          <t>Confirm the in-system notice 'Package deployment request': trigger, recipients and text (Specified).</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
@@ -14530,6 +14544,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
